--- a/outputs/evaluation/architecture/design/v2/CF_M05/run_3/CF_M05_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v2/CF_M05/run_3/CF_M05_arch_eval.xlsx
@@ -508,6 +508,8 @@
         <v>0.7829</v>
       </c>
     </row>
+    <row r="5"/>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -589,10 +591,8 @@
           <t>fixedType</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" t="n">
+        <v>0.9333</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
